--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Ratings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily Ratings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>143</v>
+        <v>130238</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>4.5</v>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>130238</v>
+        <v>143</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>4.5</v>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -1174,10 +1174,10 @@
         <v>5</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>52</v>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -634,7 +634,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16 00:00:00</t>
+          <t>16 Sept</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -671,7 +671,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 00:00:00</t>
+          <t>17 Sept</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -708,7 +708,7 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18 00:00:00</t>
+          <t>18 Sept</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -745,7 +745,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 00:00:00</t>
+          <t>19 Sept</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -782,7 +782,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00:00</t>
+          <t>20 Sept</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -819,7 +819,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 00:00:00</t>
+          <t>21 Sept</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -856,7 +856,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 00:00:00</t>
+          <t>22 Sept</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
@@ -893,7 +893,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 00:00:00</t>
+          <t>23 Sept</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
@@ -930,7 +930,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 00:00:00</t>
+          <t>24 Sept</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
@@ -967,7 +967,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 00:00:00</t>
+          <t>25 Sept</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
@@ -1004,7 +1004,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27 00:00:00</t>
+          <t>27 Sept</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
@@ -1041,7 +1041,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28 00:00:00</t>
+          <t>28 Sept</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
@@ -1078,7 +1078,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29 00:00:00</t>
+          <t>29 Sept</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
@@ -1115,7 +1115,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 00:00:00</t>
+          <t>30 Sept</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
@@ -1162,7 +1162,7 @@
         <v>4.5</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>4.4</v>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1186,6 +1186,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2 Oct</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>143</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>231</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>4.5</v>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Daily Ratings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Ratings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1186,43 +1186,6 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>2 Oct</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>144</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>231</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -28,19 +28,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Arial"/>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
@@ -54,12 +54,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8F9FA"/>
-        <bgColor rgb="00F8F9FA"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -81,26 +81,43 @@
         <color rgb="00D3D3D3"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="007F7F7F"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -470,719 +487,719 @@
   <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13.5" customWidth="1" min="1" max="1"/>
+    <col width="11.5" customWidth="1" min="2" max="2"/>
+    <col width="10.5" customWidth="1" min="3" max="3"/>
+    <col width="11.5" customWidth="1" min="4" max="4"/>
+    <col width="10.5" customWidth="1" min="5" max="5"/>
+    <col width="11.5" customWidth="1" min="6" max="6"/>
+    <col width="10.5" customWidth="1" min="7" max="7"/>
+    <col width="11.5" customWidth="1" min="8" max="8"/>
+    <col width="10.5" customWidth="1" min="9" max="9"/>
+    <col width="11.5" customWidth="1" min="10" max="10"/>
+    <col width="10.5" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Kiplings</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Casa Loco Express</t>
         </is>
       </c>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Zomato - Delivery</t>
         </is>
       </c>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Swiggy - Delivery</t>
         </is>
       </c>
-      <c r="K2" s="1" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Total no</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Rating</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Total no</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Rating</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Total no</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Rating</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Total no</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Rating</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Total no</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Rating</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>15 Sept</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>116</v>
       </c>
-      <c r="C4" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="C4" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>153</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" s="4" t="n">
+      <c r="E4" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="I4" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J4" s="4" t="n">
+      <c r="I4" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="K4" s="6" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>16 Sept</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="C5" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D5" s="5" t="n">
         <v>158</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" s="4" t="n">
+      <c r="E5" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="I5" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J5" s="4" t="n">
+      <c r="I5" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J5" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="K5" s="6" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>17 Sept</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="C6" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D6" s="5" t="n">
         <v>164</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" s="4" t="n">
+      <c r="E6" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="I6" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J6" s="4" t="n">
+      <c r="I6" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="K6" s="6" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>18 Sept</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D7" s="4" t="n">
+      <c r="C7" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>166</v>
       </c>
-      <c r="E7" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" s="4" t="n">
+      <c r="E7" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J7" s="4" t="n">
+      <c r="I7" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J7" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="K7" s="6" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>19 Sept</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D8" s="4" t="n">
+      <c r="C8" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>171</v>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" s="4" t="n">
+      <c r="E8" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="I8" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J8" s="4" t="n">
+      <c r="I8" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J8" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="K8" s="6" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>20 Sept</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="C9" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D9" s="4" t="n">
+      <c r="C9" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D9" s="5" t="n">
         <v>178</v>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" s="4" t="n">
+      <c r="E9" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="I9" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J9" s="4" t="n">
+      <c r="I9" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J9" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="K9" s="6" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>21 Sept</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="n">
         <v>123</v>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D10" s="4" t="n">
+      <c r="C10" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>187</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" s="4" t="n">
+      <c r="E10" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="I10" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J10" s="4" t="n">
+      <c r="I10" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="K10" s="6" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>22 Sept</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="5" t="n">
         <v>124</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="5" t="n">
         <v>192</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="4" t="n">
+      <c r="E11" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J11" s="4" t="n">
+      <c r="I11" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J11" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="K11" s="6" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>23 Sept</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="5" t="n">
         <v>194</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" s="4" t="n">
+      <c r="E12" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="I12" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J12" s="4" t="n">
+      <c r="I12" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="K12" s="6" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>24 Sept</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <v>124</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="5" t="n">
         <v>198</v>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" s="4" t="n">
+      <c r="E13" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="I13" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J13" s="4" t="n">
+      <c r="I13" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J13" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="K13" s="6" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>25 Sept</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="5" t="n">
         <v>129</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" s="4" t="n">
+      <c r="E14" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="6" t="n">
         <v>4.2</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="J14" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="K14" s="5" t="n">
+      <c r="K14" s="6" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>27 Sept</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="5" t="n">
         <v>142</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="5" t="n">
         <v>217</v>
       </c>
-      <c r="E15" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" s="4" t="n">
+      <c r="E15" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J15" s="4" t="n">
+      <c r="I15" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J15" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="K15" s="6" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>28 Sept</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="5" t="n">
         <v>143</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="5" t="n">
         <v>222</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H16" s="4" t="n">
+      <c r="E16" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="I16" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J16" s="4" t="n">
+      <c r="I16" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J16" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="K16" s="5" t="n">
+      <c r="K16" s="6" t="n">
         <v>3.7</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>29 Sept</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="5" t="n">
         <v>143</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="5" t="n">
         <v>225</v>
       </c>
-      <c r="E17" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" s="4" t="n">
+      <c r="E17" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="I17" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J17" s="4" t="n">
+      <c r="I17" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J17" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="K17" s="5" t="n">
+      <c r="K17" s="6" t="n">
         <v>3.7</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>30 Sept</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="5" t="n">
         <v>143</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="5" t="n">
         <v>229</v>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H18" s="4" t="n">
+      <c r="E18" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="I18" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J18" s="4" t="n">
+      <c r="I18" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J18" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="K18" s="5" t="n">
+      <c r="K18" s="6" t="n">
         <v>3.7</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>1 Oct</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
-        <v>143</v>
-      </c>
-      <c r="C19" s="5" t="n">
+      <c r="B19" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="C19" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="5" t="n">
         <v>231</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" s="4" t="n">
+      <c r="E19" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="I19" s="6" t="n">
         <v>4.2</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="K19" s="5" t="n">
+      <c r="K19" s="6" t="n">
         <v>3.7</v>
       </c>
     </row>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -614,20 +614,20 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>15 Sept</t>
+          <t>1 Oct</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="C4" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="E4" s="6" t="n">
         <v>4.4</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>153</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>4.3</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>28</v>
@@ -636,570 +636,15 @@
         <v>5</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>16 Sept</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>158</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>17 Sept</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>164</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>18 Sept</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>166</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>19 Sept</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>171</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>20 Sept</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>178</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>21 Sept</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>123</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>187</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>22 Sept</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>192</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>23 Sept</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>194</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>24 Sept</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>198</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>25 Sept</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>129</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>27 Sept</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>217</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>28 Sept</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>143</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>222</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>29 Sept</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>143</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>225</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>30 Sept</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>143</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>229</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>1 Oct</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>144</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>231</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="K19" s="6" t="n">
         <v>3.7</v>
       </c>
     </row>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Ratings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily Ratings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -648,6 +648,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2 Oct</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>237</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -685,6 +685,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>3 Oct</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>245</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -722,6 +722,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>4 Oct</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -759,6 +759,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>5 Oct</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>253</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -796,6 +796,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>6 Oct</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>257</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -833,6 +833,43 @@
         <v>3.8</v>
       </c>
     </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>7 Oct</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -870,6 +870,43 @@
         <v>3.8</v>
       </c>
     </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>8 Oct</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -907,6 +907,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>9 Oct</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -944,6 +944,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>10 Oct</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>268</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -981,6 +981,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11 Oct</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>271</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1018,6 +1018,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>12 Oct</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>274</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1055,6 +1055,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>13 Oct</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1092,6 +1092,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>14 Oct</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>284</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1129,6 +1129,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>15 Oct</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1166,6 +1166,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>16 Oct</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>286</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1203,6 +1203,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>17 Oct</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1240,6 +1240,43 @@
         <v>3.8</v>
       </c>
     </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>18 Oct</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1277,6 +1277,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>19 Oct</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>298</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1314,6 +1314,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>20 Oct</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>304</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1351,6 +1351,43 @@
         <v>3.8</v>
       </c>
     </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>21 Oct</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>305</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1388,6 +1388,43 @@
         <v>3.8</v>
       </c>
     </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>22 Oct</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>306</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1425,6 +1425,43 @@
         <v>3.8</v>
       </c>
     </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>23 Oct</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>308</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1462,6 +1462,43 @@
         <v>3.8</v>
       </c>
     </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>24 Oct</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>312</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1499,6 +1499,43 @@
         <v>3.7</v>
       </c>
     </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>25 Oct</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>313</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1536,6 +1536,39 @@
         <v>3.8</v>
       </c>
     </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>26 Oct</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>316</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1569,6 +1569,39 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr"/>
     </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>27 Oct</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>316</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1602,6 +1602,39 @@
       <c r="J30" s="4" t="inlineStr"/>
       <c r="K30" s="4" t="inlineStr"/>
     </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>28 Oct</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>318</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1635,6 +1635,43 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr"/>
     </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>29 Oct</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>319</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -1672,6 +1672,43 @@
         <v>3.8</v>
       </c>
     </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A3"/>

--- a/data/restaurant_ratings.xlsx
+++ b/data/restaurant_ratings.xlsx
@@ -1703,7 +1703,7 @@
         <v>4.3</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>3.8</v>
